--- a/Outputs/PtX_demand_IT.xlsx
+++ b/Outputs/PtX_demand_IT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,53 +488,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0036479357571302</v>
-      </c>
+      <c r="C2" t="n">
+        <v>0.06141670350059818</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02300311900116973</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.002233173391422298</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1.335177568378488e-08</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0016425518663523</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2030</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>0.0001667221954613387</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0036479357571302</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1.335177568378488e-08</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0016425518663523</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -542,7 +546,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.01272982868714951</v>
+        <v>0.0001667221954613387</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -555,14 +559,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2030</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.01272982868714951</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -574,7 +580,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -582,24 +588,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.001517032094599047</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0011196654984368</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>0.0002953533760394</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -607,14 +607,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.001517032094599047</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0140462882103178</v>
+        <v>0.0011196654984368</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.0012192777718049</v>
+        <v>0.0002953533760394</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -622,7 +624,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -631,17 +633,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0140462882103178</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.0012192777718049</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -650,29 +656,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.0696096341435164</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0005003989726162</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0147095845978992</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0576730690117931</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0004268491355289</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0250105603733093</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -682,28 +676,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.6962485521627411</v>
+        <v>0.0696096341435164</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0035241632245806</v>
+        <v>0.0005003989726162</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1305643970668376</v>
+        <v>0.0147095845978992</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3639310136313932</v>
+        <v>0.0576730690117931</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0025837187153698</v>
+        <v>0.0004268491355289</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2348176943229761</v>
+        <v>0.0250105603733093</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -711,20 +705,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.002537305967593918</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.6962485521627411</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0035241632245806</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1305643970668376</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3639310136313932</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0025837187153698</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2348176943229761</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -733,7 +737,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0006271917820834629</v>
+        <v>0.002537305967593918</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -745,96 +749,96 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>0.01289655088261085</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.004681529844276429</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.7846720757721423</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0040245621971968</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.1452739950165125</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.424761265657383</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0030105678508987</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2598282546962854</v>
-      </c>
+        <v>0.01929801489014259</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0175253502218624</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0006271917820834629</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>1.117691096132891e-06</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0023865969783612</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.06141670350059818</v>
+      </c>
       <c r="D15" t="n">
-        <v>0.0001819930503096124</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>0.03589966988378058</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.02621271812584132</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7846720757721423</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0040245621971968</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1452739950165125</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.424761265657383</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0030105678508987</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2598282546962854</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.05793355506055164</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.01389581240987423</v>
+        <v>0.007599018070426296</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -847,7 +851,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -857,12 +861,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>6.421190540173386e-09</v>
+        <v>0.0175253502218624</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1.117691096132891e-06</v>
+      </c>
       <c r="I17" t="n">
-        <v>7.404392471644982e-10</v>
+        <v>0.0023865969783612</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -870,55 +876,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2040</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.002055309681044841</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0013764905176361</v>
-      </c>
+      <c r="D18" t="n">
+        <v>0.0001819930503096124</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>0.000509620242557</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2040</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.01389581240987423</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.007613812729963001</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0.0012931202386089</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -927,17 +927,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>6.421190540173386e-09</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>7.404392471644982e-10</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -945,30 +949,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.002055309681044841</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.0325488940884981</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0008157328785995</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0191863575218352</v>
-      </c>
+        <v>0.0013764905176361</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0380820558157449</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0005185524227517</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0289957981166524</v>
-      </c>
+        <v>0.000509620242557</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -978,28 +976,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.2148972398498224</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0037886713998633</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1236661338043652</v>
-      </c>
+        <v>0.007613812729963001</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.1626073741385843</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0022928192073582</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.2253953088211194</v>
-      </c>
+        <v>0.0012931202386089</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1018,7 +1008,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1027,87 +1017,91 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0325488940884981</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0008157328785995</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0191863575218352</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0380820558157449</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0005185524227517</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0289957981166524</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2040</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
-        <v>0.01407780546018384</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.002055309681044841</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.2739617938289725</v>
+        <v>0.2148972398498224</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0046044042784628</v>
+        <v>0.0037886713998633</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1428536090172965</v>
+        <v>0.1236661338043652</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2048787681542955</v>
+        <v>0.1626073741385843</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0028113716301099</v>
+        <v>0.0022928192073582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2543911069377718</v>
+        <v>0.2253953088211194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0243107274205465</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>1.894396379722037e-06</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.003804105309536</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>0.000195852152862953</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>7.418066161335448e-19</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.003082964521567261</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1118,16 +1112,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.01495400385687069</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1139,55 +1131,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.05793355506055164</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.02167682353061014</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.005138274202612102</v>
+      </c>
       <c r="F29" t="n">
-        <v>6.040957825554191e-08</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.2739617938289725</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0046044042784628</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1428536090172965</v>
+      </c>
       <c r="I29" t="n">
-        <v>1.862117208524179e-08</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.2048787681542955</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0028113716301099</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2543911069377718</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.05477241497253818</v>
+      </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
-        <v>0.003784923913590072</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0002362118286557918</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>0.0001464881637984659</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1197,12 +1199,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>0.0004771160107088</v>
+        <v>0.0243107274205465</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>1.894396379722037e-06</v>
+      </c>
       <c r="I31" t="n">
-        <v>0.0004831337696037001</v>
+        <v>0.003804105309536</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1210,69 +1214,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2050</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0.000195852152862953</v>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>6.626646519652098e-10</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.003903291544851e-11</v>
-      </c>
-      <c r="H32" t="n">
-        <v>6.34537903847718e-10</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6.339460051053089e-10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.551475162335466e-12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.488598384219159e-09</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2050</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.01495400385687069</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0067572942771184</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0014575714346724</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0267308908885776</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.009816684255846499</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0006669405310802</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0409729797312409</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1282,28 +1266,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0388318373000604</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0034172211511031</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.106560884069033</v>
-      </c>
+        <v>6.040957825554191e-08</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0289959298007036</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0019735461906695</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.2074284198054586</v>
-      </c>
+        <v>1.862117208524179e-08</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1311,18 +1287,24 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0.003784923913590072</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0002362118286557918</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.0001464881637984659</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1331,45 +1313,203 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.0004771160107088</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0.0004831337696037001</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2050</v>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="n">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>6.626646519652098e-10</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.003903291544851e-11</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.34537903847718e-10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.339460051053089e-10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.551475162335466e-12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.488598384219159e-09</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0067572942771184</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0014575714346724</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0267308908885776</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.009816684255846499</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0006669405310802</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0409729797312409</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0388318373000604</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0034172211511031</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.106560884069033</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0289959298007036</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0019735461906695</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.2074284198054586</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>1.790567694115452e-19</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.05477241497253818</v>
+      </c>
+      <c r="D43" t="n">
         <v>0.01514985600973365</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E43" t="n">
         <v>0.003784923913590072</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F43" t="n">
         <v>0.07061324790933281</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.004874792615814533</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.1332936699885282</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.04324636055460636</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.002640486725301175</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.2484014020252979</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_IT.xlsx
+++ b/Outputs/PtX_demand_IT.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.002233173391422298</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.0806738722904795</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0202626093868865</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0254762017427467</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0038681696716766</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -728,7 +736,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -737,7 +745,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.002537305967593918</v>
+        <v>0.01929801489014259</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -749,7 +757,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -758,7 +766,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.01929801489014259</v>
+        <v>0.002537305967593918</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -807,19 +815,19 @@
         <v>0.02621271812584132</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7846720757721423</v>
+        <v>0.8653459480626218</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0040245621971968</v>
+        <v>0.0242871715840833</v>
       </c>
       <c r="H15" t="n">
         <v>0.1452739950165125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.424761265657383</v>
+        <v>0.4502374674001297</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0030105678508987</v>
+        <v>0.0068787375225753</v>
       </c>
       <c r="K15" t="n">
         <v>0.2598282546962854</v>
@@ -841,11 +849,19 @@
         <v>0.007599018070426296</v>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.2297903092048551</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0237800410695459</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0872399078572649</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0038149142102286</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1070,15 +1086,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>7.418066161335448e-19</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.003082964521567261</v>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1089,19 +1109,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
-        <v>7.418066161335448e-19</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.003082964521567261</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1147,19 +1163,19 @@
         <v>0.005138274202612102</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2739617938289725</v>
+        <v>0.5037521030338277</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0046044042784628</v>
+        <v>0.0283844453480087</v>
       </c>
       <c r="H29" t="n">
         <v>0.1428536090172965</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2048787681542955</v>
+        <v>0.2921186760115604</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0028113716301099</v>
+        <v>0.0066262858403385</v>
       </c>
       <c r="K29" t="n">
         <v>0.2543911069377718</v>
@@ -1179,11 +1195,19 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.2689485676323284</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0267048471384763</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.1292627293996196</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0038962636724318</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1420,14 +1444,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2050</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>1.790567694115452e-19</v>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1439,16 +1465,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2050</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="n">
-        <v>1.790567694115452e-19</v>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1495,19 +1519,19 @@
         <v>0.003784923913590072</v>
       </c>
       <c r="F43" t="n">
-        <v>0.07061324790933281</v>
+        <v>0.3395618155416612</v>
       </c>
       <c r="G43" t="n">
-        <v>0.004874792615814533</v>
+        <v>0.03157963975429083</v>
       </c>
       <c r="H43" t="n">
         <v>0.1332936699885282</v>
       </c>
       <c r="I43" t="n">
-        <v>0.04324636055460636</v>
+        <v>0.172509089954226</v>
       </c>
       <c r="J43" t="n">
-        <v>0.002640486725301175</v>
+        <v>0.006536750397732975</v>
       </c>
       <c r="K43" t="n">
         <v>0.2484014020252979</v>
